--- a/sample_schedule.xlsx
+++ b/sample_schedule.xlsx
@@ -827,10 +827,10 @@
         <v>Client A</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-05-05T09:00:00</v>
+        <v>2026-05-04T09:00:00</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-05-05T12:00:00</v>
+        <v>2026-05-04T12:00:00</v>
       </c>
       <c r="H2" t="str">
         <v>FALSE</v>
@@ -865,10 +865,10 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2025-05-06T14:00:00</v>
+        <v>2026-05-05T14:00:00</v>
       </c>
       <c r="G3" t="str">
-        <v>2025-05-06T15:00:00</v>
+        <v>2026-05-05T15:00:00</v>
       </c>
       <c r="H3" t="str">
         <v>FALSE</v>
@@ -903,10 +903,10 @@
         <v>Client A</v>
       </c>
       <c r="F4" t="str">
-        <v>2025-05-09T16:00:00</v>
+        <v>2026-05-08T16:00:00</v>
       </c>
       <c r="G4" t="str">
-        <v>2025-05-09T17:30:00</v>
+        <v>2026-05-08T17:30:00</v>
       </c>
       <c r="H4" t="str">
         <v>TRUE</v>

--- a/sample_schedule.xlsx
+++ b/sample_schedule.xlsx
@@ -713,7 +713,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -731,12 +731,6 @@
       <c r="E1" t="str">
         <v>parentTrainingTargetMax</v>
       </c>
-      <c r="F1" t="str">
-        <v>billableHoursPerCycle</v>
-      </c>
-      <c r="G1" t="str">
-        <v>billableCycleWeeks</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -754,16 +748,10 @@
       <c r="E2">
         <v>4</v>
       </c>
-      <c r="F2">
-        <v>80</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sample_schedule.xlsx
+++ b/sample_schedule.xlsx
@@ -841,22 +841,22 @@
         <v>APT002</v>
       </c>
       <c r="B3" t="str">
-        <v>Supervision</v>
+        <v>Supervision (Sarah / Client A)</v>
       </c>
       <c r="C3" t="str">
-        <v>Weekly supervision</v>
+        <v>Weekly supervision overlapping a direct session</v>
       </c>
       <c r="D3" t="str">
         <v>Sarah Tech</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>Client A</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-05-05T14:00:00</v>
+        <v>2026-05-04T10:00:00</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-05-05T15:00:00</v>
+        <v>2026-05-04T11:00:00</v>
       </c>
       <c r="H3" t="str">
         <v>FALSE</v>

--- a/sample_schedule.xlsx
+++ b/sample_schedule.xlsx
@@ -841,13 +841,13 @@
         <v>APT002</v>
       </c>
       <c r="B3" t="str">
-        <v>Supervision (Sarah / Client A)</v>
+        <v>Supervision — Client A</v>
       </c>
       <c r="C3" t="str">
-        <v>Weekly supervision overlapping a direct session</v>
+        <v>Weekly case supervision; tech being supervised is whoever is in session</v>
       </c>
       <c r="D3" t="str">
-        <v>Sarah Tech</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>Client A</v>
